--- a/df_group_placas.xlsx
+++ b/df_group_placas.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
+  <si>
+    <t>handle_nivel_superior</t>
+  </si>
   <si>
     <t>desc_tipo_veic</t>
   </si>
@@ -494,10 +497,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,522 +510,636 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2">
+        <v>1267</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2">
         <v>-7732.139999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
+      <c r="B3">
+        <v>1267</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3">
         <v>-5972.029999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
+      <c r="B4">
+        <v>1267</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4">
         <v>-7015.55</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>3</v>
+      <c r="B5">
+        <v>1267</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
         <v>-4446.569999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>3</v>
+      <c r="B6">
+        <v>1267</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
         <v>-2477.61</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
-        <v>3</v>
+      <c r="B7">
+        <v>1267</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7">
         <v>-155.7999999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
-        <v>3</v>
+      <c r="B8">
+        <v>1267</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
         <v>-8690.940000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
-        <v>3</v>
+      <c r="B9">
+        <v>1267</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9">
         <v>-8142.51</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>3</v>
+      <c r="B10">
+        <v>1267</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10">
         <v>-3026.65</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
-        <v>3</v>
+      <c r="B11">
+        <v>1267</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11">
         <v>-5044.59</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>3</v>
+      <c r="B12">
+        <v>1267</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12">
         <v>-5370.76</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:5">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
-        <v>3</v>
+      <c r="B13">
+        <v>1267</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13">
         <v>-11584.31</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:5">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>3</v>
+      <c r="B14">
+        <v>1267</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14">
         <v>-6543.23</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:5">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
-        <v>3</v>
+      <c r="B15">
+        <v>1267</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15">
         <v>-4751.110000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:5">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
+      <c r="B16">
+        <v>1267</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16">
         <v>-5561.57</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
+      <c r="B17">
+        <v>1267</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17">
         <v>-4709.99</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
+      <c r="B18">
+        <v>1267</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18">
         <v>-8975.5</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
+      <c r="B19">
+        <v>1267</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19">
         <v>-16.83</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
+      <c r="B20">
+        <v>1267</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20">
         <v>-16.83</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
-        <v>3</v>
+      <c r="B21">
+        <v>1267</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21">
         <v>-16.83</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>3</v>
+      <c r="B22">
+        <v>1267</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22">
         <v>-1247.37</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
-        <v>3</v>
+      <c r="B23">
+        <v>1267</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23">
         <v>-686.51</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
-        <v>3</v>
+      <c r="B24">
+        <v>1267</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24">
         <v>-6328.79</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
-        <v>3</v>
+      <c r="B25">
+        <v>1267</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25">
         <v>-1801.43</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
-        <v>3</v>
+      <c r="B26">
+        <v>1267</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26">
         <v>-1200.94</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" t="s">
-        <v>3</v>
+      <c r="B27">
+        <v>1267</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27">
         <v>-1534.22</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
+      <c r="B28">
+        <v>1267</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28">
         <v>-3097.36</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
-        <v>3</v>
+      <c r="B29">
+        <v>1267</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29">
         <v>-4697.43</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
+      <c r="B30">
+        <v>1267</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30">
         <v>-32224.18</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
-        <v>3</v>
+      <c r="B31">
+        <v>1267</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31">
         <v>-32156.85</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
-        <v>3</v>
+      <c r="B32">
+        <v>1267</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32">
         <v>-32526.2</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:5">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" t="s">
-        <v>3</v>
+      <c r="B33">
+        <v>1267</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33">
         <v>-10902.25</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:5">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
-        <v>3</v>
+      <c r="B34">
+        <v>1267</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34">
         <v>-12335.57</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:5">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
-        <v>3</v>
+      <c r="B35">
+        <v>1267</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35">
         <v>-7188.460000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:5">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" t="s">
-        <v>3</v>
+      <c r="B36">
+        <v>1267</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36">
         <v>-9564.850000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:5">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" t="s">
-        <v>3</v>
+      <c r="B37">
+        <v>1267</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37">
         <v>-9953.480000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:5">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" t="s">
-        <v>3</v>
+      <c r="B38">
+        <v>1267</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38">
         <v>-0.01</v>
       </c>
     </row>
